--- a/Data/Building/Lab.Light004.xlsx
+++ b/Data/Building/Lab.Light004.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709265453</v>
+        <v>1711858203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709275953</v>
+        <v>1711869179</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709257088</v>
+        <v>1711936192</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709266718</v>
+        <v>1711945079</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709342977</v>
+        <v>1712024569</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709354096</v>
+        <v>1712035286</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709431482</v>
+        <v>1712110985</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709442074</v>
+        <v>1712122823</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709518010</v>
+        <v>1712196611</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709527984</v>
+        <v>1712206542</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709606860</v>
+        <v>1712282696</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709616540</v>
+        <v>1712292710</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709861303</v>
+        <v>1712544952</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709870203</v>
+        <v>1712554878</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709950138</v>
+        <v>1712629025</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709959821</v>
+        <v>1712638484</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1710039430</v>
+        <v>1712714492</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1710049099</v>
+        <v>1712724670</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1710124776</v>
+        <v>1712803608</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1710136435</v>
+        <v>1712811391</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1710211064</v>
+        <v>1712888207</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1710220815</v>
+        <v>1712896232</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1710468305</v>
+        <v>1713146886</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1710478342</v>
+        <v>1713157022</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710555643</v>
+        <v>1713231949</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710565188</v>
+        <v>1713241288</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710645288</v>
+        <v>1713318614</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710656344</v>
+        <v>1713326267</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710729101</v>
+        <v>1713403762</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710738285</v>
+        <v>1713412094</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710814634</v>
+        <v>1713493139</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710825818</v>
+        <v>1713501241</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1711073062</v>
+        <v>1713749014</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1711084011</v>
+        <v>1713757283</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1711160284</v>
+        <v>1713838921</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1711172643</v>
+        <v>1713849342</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1711245452</v>
+        <v>1713923644</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1711255818</v>
+        <v>1713932290</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1711331380</v>
+        <v>1714007147</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1711339671</v>
+        <v>1714016921</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1711420397</v>
+        <v>1714093860</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1711430250</v>
+        <v>1714102841</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
